--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589849</v>
+        <v>121589860</v>
       </c>
       <c r="B2" t="n">
-        <v>79719</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651041</v>
+        <v>650830</v>
       </c>
       <c r="R2" t="n">
-        <v>7170695</v>
+        <v>7170622</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589844</v>
+        <v>121589840</v>
       </c>
       <c r="B3" t="n">
-        <v>90886</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1588</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,16 +819,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651065</v>
+        <v>651113</v>
       </c>
       <c r="R3" t="n">
-        <v>7170686</v>
+        <v>7170655</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,6 +869,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589835</v>
+        <v>121589844</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>90886</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +912,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1588</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651023</v>
+        <v>651065</v>
       </c>
       <c r="R4" t="n">
-        <v>7170755</v>
+        <v>7170686</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589842</v>
+        <v>121589841</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651053</v>
+        <v>651098</v>
       </c>
       <c r="R5" t="n">
-        <v>7170636</v>
+        <v>7170643</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589819</v>
+        <v>121589856</v>
       </c>
       <c r="B6" t="n">
-        <v>79725</v>
+        <v>98022</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650739</v>
+        <v>650844</v>
       </c>
       <c r="R6" t="n">
-        <v>7170646</v>
+        <v>7170673</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589865</v>
+        <v>121589830</v>
       </c>
       <c r="B7" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650742</v>
+        <v>650815</v>
       </c>
       <c r="R7" t="n">
-        <v>7170597</v>
+        <v>7170874</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,11 +1298,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1324,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589845</v>
+        <v>121589853</v>
       </c>
       <c r="B8" t="n">
         <v>79726</v>
@@ -1360,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651040</v>
+        <v>650880</v>
       </c>
       <c r="R8" t="n">
-        <v>7170672</v>
+        <v>7170682</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1396,11 +1404,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589860</v>
+        <v>121589843</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,30 +1442,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1471,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650830</v>
+        <v>651069</v>
       </c>
       <c r="R9" t="n">
-        <v>7170622</v>
+        <v>7170647</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589839</v>
+        <v>121589851</v>
       </c>
       <c r="B10" t="n">
         <v>79690</v>
@@ -1577,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651123</v>
+        <v>650992</v>
       </c>
       <c r="R10" t="n">
-        <v>7170655</v>
+        <v>7170679</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1639,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589817</v>
+        <v>121589838</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>79719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,30 +1654,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1683,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650754</v>
+        <v>651123</v>
       </c>
       <c r="R11" t="n">
-        <v>7170637</v>
+        <v>7170655</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589856</v>
+        <v>121589845</v>
       </c>
       <c r="B12" t="n">
-        <v>98022</v>
+        <v>79726</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1764,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650844</v>
+        <v>651040</v>
       </c>
       <c r="R12" t="n">
-        <v>7170673</v>
+        <v>7170672</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,6 +1828,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589863</v>
+        <v>121589820</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,21 +1875,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650786</v>
+        <v>650739</v>
       </c>
       <c r="R13" t="n">
-        <v>7170620</v>
+        <v>7170646</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1957,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589846</v>
+        <v>121589858</v>
       </c>
       <c r="B14" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,30 +1977,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2001,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651020</v>
+        <v>650846</v>
       </c>
       <c r="R14" t="n">
-        <v>7170657</v>
+        <v>7170647</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2037,11 +2045,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589843</v>
+        <v>121589861</v>
       </c>
       <c r="B15" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,30 +2083,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2112,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651069</v>
+        <v>650816</v>
       </c>
       <c r="R15" t="n">
-        <v>7170647</v>
+        <v>7170626</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2148,6 +2151,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,10 +2182,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589830</v>
+        <v>121589852</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,30 +2194,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2218,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650815</v>
+        <v>650913</v>
       </c>
       <c r="R16" t="n">
-        <v>7170874</v>
+        <v>7170668</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2280,10 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589848</v>
+        <v>121589832</v>
       </c>
       <c r="B17" t="n">
-        <v>79690</v>
+        <v>90886</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,21 +2304,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2324,10 +2332,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651044</v>
+        <v>650886</v>
       </c>
       <c r="R17" t="n">
-        <v>7170685</v>
+        <v>7170833</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2386,10 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589850</v>
+        <v>121589817</v>
       </c>
       <c r="B18" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,30 +2406,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2430,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651040</v>
+        <v>650754</v>
       </c>
       <c r="R18" t="n">
-        <v>7170694</v>
+        <v>7170637</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2492,10 +2500,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589864</v>
+        <v>121589863</v>
       </c>
       <c r="B19" t="n">
-        <v>79726</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,25 +2512,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2536,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650742</v>
+        <v>650786</v>
       </c>
       <c r="R19" t="n">
-        <v>7170597</v>
+        <v>7170620</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2598,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589858</v>
+        <v>121589848</v>
       </c>
       <c r="B20" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,30 +2618,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2642,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650846</v>
+        <v>651044</v>
       </c>
       <c r="R20" t="n">
-        <v>7170647</v>
+        <v>7170685</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2704,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589831</v>
+        <v>121589833</v>
       </c>
       <c r="B21" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,30 +2724,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2748,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650882</v>
+        <v>650931</v>
       </c>
       <c r="R21" t="n">
-        <v>7170828</v>
+        <v>7170785</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2810,10 +2818,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589828</v>
+        <v>121589819</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>79725</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2822,20 +2830,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2854,10 +2862,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650645</v>
+        <v>650739</v>
       </c>
       <c r="R22" t="n">
-        <v>7170985</v>
+        <v>7170646</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2916,10 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589847</v>
+        <v>121589839</v>
       </c>
       <c r="B23" t="n">
-        <v>79725</v>
+        <v>79690</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,25 +2936,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2960,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651045</v>
+        <v>651123</v>
       </c>
       <c r="R23" t="n">
-        <v>7170684</v>
+        <v>7170655</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3022,10 +3030,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589859</v>
+        <v>121589834</v>
       </c>
       <c r="B24" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3038,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3066,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650836</v>
+        <v>650935</v>
       </c>
       <c r="R24" t="n">
-        <v>7170651</v>
+        <v>7170775</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3128,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589832</v>
+        <v>121589849</v>
       </c>
       <c r="B25" t="n">
-        <v>90886</v>
+        <v>79719</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,25 +3148,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1588</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3172,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650886</v>
+        <v>651041</v>
       </c>
       <c r="R25" t="n">
-        <v>7170833</v>
+        <v>7170695</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3234,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589838</v>
+        <v>121589855</v>
       </c>
       <c r="B26" t="n">
-        <v>79719</v>
+        <v>79690</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3246,25 +3254,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3278,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651123</v>
+        <v>650892</v>
       </c>
       <c r="R26" t="n">
-        <v>7170655</v>
+        <v>7170693</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3314,6 +3322,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,10 +3353,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589837</v>
+        <v>121589854</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3352,25 +3365,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3384,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651072</v>
+        <v>650895</v>
       </c>
       <c r="R27" t="n">
-        <v>7170724</v>
+        <v>7170701</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3446,10 +3459,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589854</v>
+        <v>121589829</v>
       </c>
       <c r="B28" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,25 +3471,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3490,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650895</v>
+        <v>650789</v>
       </c>
       <c r="R28" t="n">
-        <v>7170701</v>
+        <v>7170866</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3552,10 +3565,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589855</v>
+        <v>121589857</v>
       </c>
       <c r="B29" t="n">
-        <v>79690</v>
+        <v>90716</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3568,21 +3581,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3596,10 +3609,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650892</v>
+        <v>650826</v>
       </c>
       <c r="R29" t="n">
-        <v>7170693</v>
+        <v>7170658</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3636,7 +3649,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Växer pa grov sälg</t>
+          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3663,10 +3676,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121589833</v>
+        <v>121589837</v>
       </c>
       <c r="B30" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3675,30 +3688,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3707,10 +3720,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650931</v>
+        <v>651072</v>
       </c>
       <c r="R30" t="n">
-        <v>7170785</v>
+        <v>7170724</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3769,10 +3782,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121589818</v>
+        <v>121589850</v>
       </c>
       <c r="B31" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3781,30 +3794,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3813,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650745</v>
+        <v>651040</v>
       </c>
       <c r="R31" t="n">
-        <v>7170644</v>
+        <v>7170694</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3875,10 +3888,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121589853</v>
+        <v>121589862</v>
       </c>
       <c r="B32" t="n">
-        <v>79726</v>
+        <v>78609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3887,25 +3900,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3919,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650880</v>
+        <v>650799</v>
       </c>
       <c r="R32" t="n">
-        <v>7170682</v>
+        <v>7170628</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3981,10 +3994,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121589861</v>
+        <v>121589842</v>
       </c>
       <c r="B33" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3993,30 +4006,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4025,10 +4038,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650816</v>
+        <v>651053</v>
       </c>
       <c r="R33" t="n">
-        <v>7170626</v>
+        <v>7170636</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4061,11 +4074,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4092,10 +4100,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121589840</v>
+        <v>121589846</v>
       </c>
       <c r="B34" t="n">
-        <v>57509</v>
+        <v>79690</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4108,21 +4116,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4130,24 +4138,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651113</v>
+        <v>651020</v>
       </c>
       <c r="R34" t="n">
-        <v>7170655</v>
+        <v>7170657</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4317,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121589857</v>
+        <v>121589865</v>
       </c>
       <c r="B36" t="n">
-        <v>90716</v>
+        <v>79690</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4333,21 +4333,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650826</v>
+        <v>650742</v>
       </c>
       <c r="R36" t="n">
-        <v>7170658</v>
+        <v>7170597</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar på stående död gran</t>
+          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4428,10 +4428,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121589851</v>
+        <v>121589831</v>
       </c>
       <c r="B37" t="n">
-        <v>79690</v>
+        <v>90738</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4444,21 +4444,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650992</v>
+        <v>650882</v>
       </c>
       <c r="R37" t="n">
-        <v>7170679</v>
+        <v>7170828</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121589834</v>
+        <v>121589847</v>
       </c>
       <c r="B38" t="n">
-        <v>78609</v>
+        <v>79725</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,20 +4546,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650935</v>
+        <v>651045</v>
       </c>
       <c r="R38" t="n">
-        <v>7170775</v>
+        <v>7170684</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4640,10 +4640,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121589841</v>
+        <v>121589818</v>
       </c>
       <c r="B39" t="n">
-        <v>79691</v>
+        <v>98105</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,30 +4652,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651098</v>
+        <v>650745</v>
       </c>
       <c r="R39" t="n">
-        <v>7170643</v>
+        <v>7170644</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4746,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121589829</v>
+        <v>121589864</v>
       </c>
       <c r="B40" t="n">
-        <v>78609</v>
+        <v>79726</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4758,25 +4758,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650789</v>
+        <v>650742</v>
       </c>
       <c r="R40" t="n">
-        <v>7170866</v>
+        <v>7170597</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4852,7 +4852,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121589862</v>
+        <v>121589828</v>
       </c>
       <c r="B41" t="n">
         <v>78609</v>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650799</v>
+        <v>650645</v>
       </c>
       <c r="R41" t="n">
-        <v>7170628</v>
+        <v>7170985</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4958,10 +4958,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121589820</v>
+        <v>121589859</v>
       </c>
       <c r="B42" t="n">
-        <v>79690</v>
+        <v>90716</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650739</v>
+        <v>650836</v>
       </c>
       <c r="R42" t="n">
-        <v>7170646</v>
+        <v>7170651</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121589852</v>
+        <v>121589835</v>
       </c>
       <c r="B43" t="n">
-        <v>98105</v>
+        <v>97059</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5076,30 +5076,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650913</v>
+        <v>651023</v>
       </c>
       <c r="R43" t="n">
-        <v>7170668</v>
+        <v>7170755</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>

--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589860</v>
+        <v>121589817</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650830</v>
+        <v>650754</v>
       </c>
       <c r="R2" t="n">
-        <v>7170622</v>
+        <v>7170637</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589840</v>
+        <v>121589859</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>90716</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,24 +819,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651113</v>
+        <v>650836</v>
       </c>
       <c r="R3" t="n">
-        <v>7170655</v>
+        <v>7170651</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1006,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589841</v>
+        <v>121589832</v>
       </c>
       <c r="B5" t="n">
-        <v>79691</v>
+        <v>90886</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1588</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1050,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651098</v>
+        <v>650886</v>
       </c>
       <c r="R5" t="n">
-        <v>7170643</v>
+        <v>7170833</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589856</v>
+        <v>121589828</v>
       </c>
       <c r="B6" t="n">
-        <v>98022</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1156,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650844</v>
+        <v>650645</v>
       </c>
       <c r="R6" t="n">
-        <v>7170673</v>
+        <v>7170985</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589830</v>
+        <v>121589848</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1262,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650815</v>
+        <v>651044</v>
       </c>
       <c r="R7" t="n">
-        <v>7170874</v>
+        <v>7170685</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589853</v>
+        <v>121589838</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
+        <v>79719</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1368,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650880</v>
+        <v>651123</v>
       </c>
       <c r="R8" t="n">
-        <v>7170682</v>
+        <v>7170655</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1430,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589843</v>
+        <v>121589845</v>
       </c>
       <c r="B9" t="n">
-        <v>79690</v>
+        <v>79726</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1474,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651069</v>
+        <v>651040</v>
       </c>
       <c r="R9" t="n">
-        <v>7170647</v>
+        <v>7170672</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1510,6 +1497,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589851</v>
+        <v>121589837</v>
       </c>
       <c r="B10" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1580,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650992</v>
+        <v>651072</v>
       </c>
       <c r="R10" t="n">
-        <v>7170679</v>
+        <v>7170724</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1642,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589838</v>
+        <v>121589829</v>
       </c>
       <c r="B11" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1686,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651123</v>
+        <v>650789</v>
       </c>
       <c r="R11" t="n">
-        <v>7170655</v>
+        <v>7170866</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589845</v>
+        <v>121589858</v>
       </c>
       <c r="B12" t="n">
-        <v>79726</v>
+        <v>98105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,30 +1752,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1792,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651040</v>
+        <v>650846</v>
       </c>
       <c r="R12" t="n">
-        <v>7170672</v>
+        <v>7170647</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1828,11 +1820,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589820</v>
+        <v>121589860</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1871,30 +1858,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1903,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650739</v>
+        <v>650830</v>
       </c>
       <c r="R13" t="n">
-        <v>7170646</v>
+        <v>7170622</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1965,7 +1952,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589858</v>
+        <v>121589852</v>
       </c>
       <c r="B14" t="n">
         <v>98105</v>
@@ -2000,7 +1987,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2009,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650846</v>
+        <v>650913</v>
       </c>
       <c r="R14" t="n">
-        <v>7170647</v>
+        <v>7170668</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2071,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589861</v>
+        <v>121589854</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>79719</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,30 +2070,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2115,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650816</v>
+        <v>650895</v>
       </c>
       <c r="R15" t="n">
-        <v>7170626</v>
+        <v>7170701</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2151,11 +2138,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589852</v>
+        <v>121589820</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,30 +2176,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2226,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650913</v>
+        <v>650739</v>
       </c>
       <c r="R16" t="n">
-        <v>7170668</v>
+        <v>7170646</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2288,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589832</v>
+        <v>121589839</v>
       </c>
       <c r="B17" t="n">
-        <v>90886</v>
+        <v>79690</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2304,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1588</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2332,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650886</v>
+        <v>651123</v>
       </c>
       <c r="R17" t="n">
-        <v>7170833</v>
+        <v>7170655</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2394,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589817</v>
+        <v>121589835</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
+        <v>97059</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2406,30 +2388,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2438,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650754</v>
+        <v>651023</v>
       </c>
       <c r="R18" t="n">
-        <v>7170637</v>
+        <v>7170755</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2606,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589848</v>
+        <v>121589864</v>
       </c>
       <c r="B20" t="n">
-        <v>79690</v>
+        <v>79726</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2618,25 +2600,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2650,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651044</v>
+        <v>650742</v>
       </c>
       <c r="R20" t="n">
-        <v>7170685</v>
+        <v>7170597</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2712,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589833</v>
+        <v>121589849</v>
       </c>
       <c r="B21" t="n">
-        <v>98105</v>
+        <v>79719</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,30 +2706,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2756,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650931</v>
+        <v>651041</v>
       </c>
       <c r="R21" t="n">
-        <v>7170785</v>
+        <v>7170695</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2818,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589819</v>
+        <v>121589853</v>
       </c>
       <c r="B22" t="n">
-        <v>79725</v>
+        <v>79726</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2834,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2862,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650739</v>
+        <v>650880</v>
       </c>
       <c r="R22" t="n">
-        <v>7170646</v>
+        <v>7170682</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2924,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589839</v>
+        <v>121589818</v>
       </c>
       <c r="B23" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,30 +2918,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2968,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651123</v>
+        <v>650745</v>
       </c>
       <c r="R23" t="n">
-        <v>7170655</v>
+        <v>7170644</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3030,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589834</v>
+        <v>121589841</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3046,21 +3028,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3074,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650935</v>
+        <v>651098</v>
       </c>
       <c r="R24" t="n">
-        <v>7170775</v>
+        <v>7170643</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3136,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589849</v>
+        <v>121589843</v>
       </c>
       <c r="B25" t="n">
-        <v>79719</v>
+        <v>79690</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3148,25 +3130,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3180,10 +3162,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651041</v>
+        <v>651069</v>
       </c>
       <c r="R25" t="n">
-        <v>7170695</v>
+        <v>7170647</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3242,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589855</v>
+        <v>121589847</v>
       </c>
       <c r="B26" t="n">
-        <v>79690</v>
+        <v>79725</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3254,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3286,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650892</v>
+        <v>651045</v>
       </c>
       <c r="R26" t="n">
-        <v>7170693</v>
+        <v>7170684</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3322,11 +3304,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589854</v>
+        <v>121589851</v>
       </c>
       <c r="B27" t="n">
-        <v>79719</v>
+        <v>79690</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,25 +3342,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3397,10 +3374,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650895</v>
+        <v>650992</v>
       </c>
       <c r="R27" t="n">
-        <v>7170701</v>
+        <v>7170679</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3459,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589829</v>
+        <v>121589861</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3471,30 +3448,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3503,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650789</v>
+        <v>650816</v>
       </c>
       <c r="R28" t="n">
-        <v>7170866</v>
+        <v>7170626</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3539,6 +3516,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3565,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589857</v>
+        <v>121589865</v>
       </c>
       <c r="B29" t="n">
-        <v>90716</v>
+        <v>79690</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3581,21 +3563,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3609,10 +3591,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650826</v>
+        <v>650742</v>
       </c>
       <c r="R29" t="n">
-        <v>7170658</v>
+        <v>7170597</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3649,7 +3631,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar på stående död gran</t>
+          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3676,10 +3658,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121589837</v>
+        <v>121589831</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3692,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3720,10 +3702,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651072</v>
+        <v>650882</v>
       </c>
       <c r="R30" t="n">
-        <v>7170724</v>
+        <v>7170828</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3782,10 +3764,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121589850</v>
+        <v>121589857</v>
       </c>
       <c r="B31" t="n">
-        <v>79690</v>
+        <v>90716</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3798,21 +3780,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3826,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651040</v>
+        <v>650826</v>
       </c>
       <c r="R31" t="n">
-        <v>7170694</v>
+        <v>7170658</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3862,6 +3844,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3888,7 +3875,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121589862</v>
+        <v>121589834</v>
       </c>
       <c r="B32" t="n">
         <v>78609</v>
@@ -3932,10 +3919,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650799</v>
+        <v>650935</v>
       </c>
       <c r="R32" t="n">
-        <v>7170628</v>
+        <v>7170775</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4100,10 +4087,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121589846</v>
+        <v>121589833</v>
       </c>
       <c r="B34" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4112,30 +4099,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4144,10 +4131,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651020</v>
+        <v>650931</v>
       </c>
       <c r="R34" t="n">
-        <v>7170657</v>
+        <v>7170785</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4180,11 +4167,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4211,10 +4193,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121589836</v>
+        <v>121589830</v>
       </c>
       <c r="B35" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4227,21 +4209,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4255,10 +4237,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651064</v>
+        <v>650815</v>
       </c>
       <c r="R35" t="n">
-        <v>7170712</v>
+        <v>7170874</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4317,10 +4299,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121589865</v>
+        <v>121589836</v>
       </c>
       <c r="B36" t="n">
-        <v>79690</v>
+        <v>90738</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4333,21 +4315,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4361,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650742</v>
+        <v>651064</v>
       </c>
       <c r="R36" t="n">
-        <v>7170597</v>
+        <v>7170712</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4397,11 +4379,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4428,10 +4405,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121589831</v>
+        <v>121589855</v>
       </c>
       <c r="B37" t="n">
-        <v>90738</v>
+        <v>79690</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4444,21 +4421,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4472,10 +4449,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650882</v>
+        <v>650892</v>
       </c>
       <c r="R37" t="n">
-        <v>7170828</v>
+        <v>7170693</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4508,6 +4485,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,10 +4516,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121589847</v>
+        <v>121589846</v>
       </c>
       <c r="B38" t="n">
-        <v>79725</v>
+        <v>79690</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,25 +4528,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4578,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651045</v>
+        <v>651020</v>
       </c>
       <c r="R38" t="n">
-        <v>7170684</v>
+        <v>7170657</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4614,6 +4596,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4640,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121589818</v>
+        <v>121589819</v>
       </c>
       <c r="B39" t="n">
-        <v>98105</v>
+        <v>79725</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,30 +4639,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4684,10 +4671,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650745</v>
+        <v>650739</v>
       </c>
       <c r="R39" t="n">
-        <v>7170644</v>
+        <v>7170646</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4746,10 +4733,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121589864</v>
+        <v>121589840</v>
       </c>
       <c r="B40" t="n">
-        <v>79726</v>
+        <v>57509</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4758,25 +4745,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4784,16 +4771,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650742</v>
+        <v>651113</v>
       </c>
       <c r="R40" t="n">
-        <v>7170597</v>
+        <v>7170655</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4826,6 +4821,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4852,10 +4852,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121589828</v>
+        <v>121589856</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
+        <v>98022</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4864,25 +4864,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650645</v>
+        <v>650844</v>
       </c>
       <c r="R41" t="n">
-        <v>7170985</v>
+        <v>7170673</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4958,10 +4958,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121589859</v>
+        <v>121589850</v>
       </c>
       <c r="B42" t="n">
-        <v>90716</v>
+        <v>79690</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650836</v>
+        <v>651040</v>
       </c>
       <c r="R42" t="n">
-        <v>7170651</v>
+        <v>7170694</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121589835</v>
+        <v>121589862</v>
       </c>
       <c r="B43" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5076,25 +5076,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651023</v>
+        <v>650799</v>
       </c>
       <c r="R43" t="n">
-        <v>7170755</v>
+        <v>7170628</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>

--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589859</v>
+        <v>121589828</v>
       </c>
       <c r="B3" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650836</v>
+        <v>650645</v>
       </c>
       <c r="R3" t="n">
-        <v>7170651</v>
+        <v>7170985</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589844</v>
+        <v>121589848</v>
       </c>
       <c r="B4" t="n">
-        <v>90886</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1588</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651065</v>
+        <v>651044</v>
       </c>
       <c r="R4" t="n">
-        <v>7170686</v>
+        <v>7170685</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589832</v>
+        <v>121589859</v>
       </c>
       <c r="B5" t="n">
-        <v>90886</v>
+        <v>90716</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1588</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650886</v>
+        <v>650836</v>
       </c>
       <c r="R5" t="n">
-        <v>7170833</v>
+        <v>7170651</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589828</v>
+        <v>121589844</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>90886</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650645</v>
+        <v>651065</v>
       </c>
       <c r="R6" t="n">
-        <v>7170985</v>
+        <v>7170686</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589848</v>
+        <v>121589832</v>
       </c>
       <c r="B7" t="n">
-        <v>79690</v>
+        <v>90886</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651044</v>
+        <v>650886</v>
       </c>
       <c r="R7" t="n">
-        <v>7170685</v>
+        <v>7170833</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589820</v>
+        <v>121589835</v>
       </c>
       <c r="B16" t="n">
-        <v>79690</v>
+        <v>97059</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650739</v>
+        <v>651023</v>
       </c>
       <c r="R16" t="n">
-        <v>7170646</v>
+        <v>7170755</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589839</v>
+        <v>121589820</v>
       </c>
       <c r="B17" t="n">
         <v>79690</v>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651123</v>
+        <v>650739</v>
       </c>
       <c r="R17" t="n">
-        <v>7170655</v>
+        <v>7170646</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589835</v>
+        <v>121589839</v>
       </c>
       <c r="B18" t="n">
-        <v>97059</v>
+        <v>79690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651023</v>
+        <v>651123</v>
       </c>
       <c r="R18" t="n">
-        <v>7170755</v>
+        <v>7170655</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589843</v>
+        <v>121589847</v>
       </c>
       <c r="B25" t="n">
-        <v>79690</v>
+        <v>79725</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3130,25 +3130,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651069</v>
+        <v>651045</v>
       </c>
       <c r="R25" t="n">
-        <v>7170647</v>
+        <v>7170684</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589847</v>
+        <v>121589843</v>
       </c>
       <c r="B26" t="n">
-        <v>79725</v>
+        <v>79690</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3236,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651045</v>
+        <v>651069</v>
       </c>
       <c r="R26" t="n">
-        <v>7170684</v>
+        <v>7170647</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589828</v>
+        <v>121589859</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650645</v>
+        <v>650836</v>
       </c>
       <c r="R3" t="n">
-        <v>7170985</v>
+        <v>7170651</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589848</v>
+        <v>121589844</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>90886</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651044</v>
+        <v>651065</v>
       </c>
       <c r="R4" t="n">
-        <v>7170685</v>
+        <v>7170686</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589859</v>
+        <v>121589832</v>
       </c>
       <c r="B5" t="n">
-        <v>90716</v>
+        <v>90886</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1588</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650836</v>
+        <v>650886</v>
       </c>
       <c r="R5" t="n">
-        <v>7170651</v>
+        <v>7170833</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589844</v>
+        <v>121589838</v>
       </c>
       <c r="B6" t="n">
-        <v>90886</v>
+        <v>79719</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1588</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651065</v>
+        <v>651123</v>
       </c>
       <c r="R6" t="n">
-        <v>7170686</v>
+        <v>7170655</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589832</v>
+        <v>121589828</v>
       </c>
       <c r="B7" t="n">
-        <v>90886</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650886</v>
+        <v>650645</v>
       </c>
       <c r="R7" t="n">
-        <v>7170833</v>
+        <v>7170985</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589838</v>
+        <v>121589848</v>
       </c>
       <c r="B8" t="n">
-        <v>79719</v>
+        <v>79690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651123</v>
+        <v>651044</v>
       </c>
       <c r="R8" t="n">
-        <v>7170655</v>
+        <v>7170685</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589847</v>
+        <v>121589843</v>
       </c>
       <c r="B25" t="n">
-        <v>79725</v>
+        <v>79690</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3130,25 +3130,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651045</v>
+        <v>651069</v>
       </c>
       <c r="R25" t="n">
-        <v>7170684</v>
+        <v>7170647</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589843</v>
+        <v>121589847</v>
       </c>
       <c r="B26" t="n">
-        <v>79690</v>
+        <v>79725</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3236,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651069</v>
+        <v>651045</v>
       </c>
       <c r="R26" t="n">
-        <v>7170647</v>
+        <v>7170684</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4405,10 +4405,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121589855</v>
+        <v>121589819</v>
       </c>
       <c r="B37" t="n">
-        <v>79690</v>
+        <v>79725</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4417,25 +4417,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650892</v>
+        <v>650739</v>
       </c>
       <c r="R37" t="n">
-        <v>7170693</v>
+        <v>7170646</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4485,11 +4485,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4516,10 +4511,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121589846</v>
+        <v>121589840</v>
       </c>
       <c r="B38" t="n">
-        <v>79690</v>
+        <v>57509</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4532,21 +4527,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4554,16 +4549,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651020</v>
+        <v>651113</v>
       </c>
       <c r="R38" t="n">
-        <v>7170657</v>
+        <v>7170655</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4600,7 +4603,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växer på rönn</t>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4627,10 +4630,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121589819</v>
+        <v>121589856</v>
       </c>
       <c r="B39" t="n">
-        <v>79725</v>
+        <v>98022</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4643,21 +4646,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4671,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650739</v>
+        <v>650844</v>
       </c>
       <c r="R39" t="n">
-        <v>7170646</v>
+        <v>7170673</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4733,10 +4736,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121589840</v>
+        <v>121589855</v>
       </c>
       <c r="B40" t="n">
-        <v>57509</v>
+        <v>79690</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4749,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4771,24 +4774,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651113</v>
+        <v>650892</v>
       </c>
       <c r="R40" t="n">
-        <v>7170655</v>
+        <v>7170693</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4825,7 +4820,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4852,10 +4847,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121589856</v>
+        <v>121589846</v>
       </c>
       <c r="B41" t="n">
-        <v>98022</v>
+        <v>79690</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4864,25 +4859,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4896,10 +4891,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650844</v>
+        <v>651020</v>
       </c>
       <c r="R41" t="n">
-        <v>7170673</v>
+        <v>7170657</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4932,6 +4927,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589817</v>
+        <v>121589832</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>90894</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650754</v>
+        <v>650886</v>
       </c>
       <c r="R2" t="n">
-        <v>7170637</v>
+        <v>7170833</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589859</v>
+        <v>121589831</v>
       </c>
       <c r="B3" t="n">
-        <v>90716</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650836</v>
+        <v>650882</v>
       </c>
       <c r="R3" t="n">
-        <v>7170651</v>
+        <v>7170828</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,7 +890,7 @@
         <v>121589844</v>
       </c>
       <c r="B4" t="n">
-        <v>90886</v>
+        <v>90894</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589832</v>
+        <v>121589856</v>
       </c>
       <c r="B5" t="n">
-        <v>90886</v>
+        <v>98030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1588</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650886</v>
+        <v>650844</v>
       </c>
       <c r="R5" t="n">
-        <v>7170833</v>
+        <v>7170673</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589838</v>
+        <v>121589843</v>
       </c>
       <c r="B6" t="n">
-        <v>79719</v>
+        <v>79697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651123</v>
+        <v>651069</v>
       </c>
       <c r="R6" t="n">
-        <v>7170655</v>
+        <v>7170647</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589828</v>
+        <v>121589818</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,30 +1217,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650645</v>
+        <v>650745</v>
       </c>
       <c r="R7" t="n">
-        <v>7170985</v>
+        <v>7170644</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589848</v>
+        <v>121589860</v>
       </c>
       <c r="B8" t="n">
-        <v>79690</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,30 +1323,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651044</v>
+        <v>650830</v>
       </c>
       <c r="R8" t="n">
-        <v>7170685</v>
+        <v>7170622</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589845</v>
+        <v>121589857</v>
       </c>
       <c r="B9" t="n">
-        <v>79726</v>
+        <v>90724</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651040</v>
+        <v>650826</v>
       </c>
       <c r="R9" t="n">
-        <v>7170672</v>
+        <v>7170658</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer på rönn</t>
+          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589837</v>
+        <v>121589819</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>79732</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,20 +1540,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651072</v>
+        <v>650739</v>
       </c>
       <c r="R10" t="n">
-        <v>7170724</v>
+        <v>7170646</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589829</v>
+        <v>121589864</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>79733</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650789</v>
+        <v>650742</v>
       </c>
       <c r="R11" t="n">
-        <v>7170866</v>
+        <v>7170597</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589858</v>
+        <v>121589853</v>
       </c>
       <c r="B12" t="n">
-        <v>98105</v>
+        <v>79733</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,30 +1752,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650846</v>
+        <v>650880</v>
       </c>
       <c r="R12" t="n">
-        <v>7170647</v>
+        <v>7170682</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589860</v>
+        <v>121589847</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
+        <v>79732</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,30 +1858,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650830</v>
+        <v>651045</v>
       </c>
       <c r="R13" t="n">
-        <v>7170622</v>
+        <v>7170684</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589852</v>
+        <v>121589862</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,30 +1964,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650913</v>
+        <v>650799</v>
       </c>
       <c r="R14" t="n">
-        <v>7170668</v>
+        <v>7170628</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589854</v>
+        <v>121589855</v>
       </c>
       <c r="B15" t="n">
-        <v>79719</v>
+        <v>79697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650895</v>
+        <v>650892</v>
       </c>
       <c r="R15" t="n">
-        <v>7170701</v>
+        <v>7170693</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2138,6 +2138,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589835</v>
+        <v>121589833</v>
       </c>
       <c r="B16" t="n">
-        <v>97059</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,30 +2181,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2208,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651023</v>
+        <v>650931</v>
       </c>
       <c r="R16" t="n">
-        <v>7170755</v>
+        <v>7170785</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2270,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589820</v>
+        <v>121589834</v>
       </c>
       <c r="B17" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2314,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650739</v>
+        <v>650935</v>
       </c>
       <c r="R17" t="n">
-        <v>7170646</v>
+        <v>7170775</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2376,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589839</v>
+        <v>121589865</v>
       </c>
       <c r="B18" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651123</v>
+        <v>650742</v>
       </c>
       <c r="R18" t="n">
-        <v>7170655</v>
+        <v>7170597</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2456,6 +2461,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589863</v>
+        <v>121589859</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>90724</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2508,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2526,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650786</v>
+        <v>650836</v>
       </c>
       <c r="R19" t="n">
-        <v>7170620</v>
+        <v>7170651</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2588,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589864</v>
+        <v>121589841</v>
       </c>
       <c r="B20" t="n">
-        <v>79726</v>
+        <v>79698</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,25 +2610,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2632,10 +2642,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650742</v>
+        <v>651098</v>
       </c>
       <c r="R20" t="n">
-        <v>7170597</v>
+        <v>7170643</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589849</v>
+        <v>121589845</v>
       </c>
       <c r="B21" t="n">
-        <v>79719</v>
+        <v>79733</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,21 +2720,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2738,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651041</v>
+        <v>651040</v>
       </c>
       <c r="R21" t="n">
-        <v>7170695</v>
+        <v>7170672</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2774,6 +2784,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589853</v>
+        <v>121589861</v>
       </c>
       <c r="B22" t="n">
-        <v>79726</v>
+        <v>98113</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,30 +2827,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2844,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650880</v>
+        <v>650816</v>
       </c>
       <c r="R22" t="n">
-        <v>7170682</v>
+        <v>7170626</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2880,6 +2895,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2906,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589818</v>
+        <v>121589835</v>
       </c>
       <c r="B23" t="n">
-        <v>98105</v>
+        <v>97067</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,30 +2938,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2950,10 +2970,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650745</v>
+        <v>651023</v>
       </c>
       <c r="R23" t="n">
-        <v>7170644</v>
+        <v>7170755</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589841</v>
+        <v>121589846</v>
       </c>
       <c r="B24" t="n">
-        <v>79691</v>
+        <v>79697</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3028,21 +3048,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3056,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651098</v>
+        <v>651020</v>
       </c>
       <c r="R24" t="n">
-        <v>7170643</v>
+        <v>7170657</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3092,6 +3112,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,10 +3143,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589843</v>
+        <v>121589858</v>
       </c>
       <c r="B25" t="n">
-        <v>79690</v>
+        <v>98113</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3130,30 +3155,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3162,7 +3187,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651069</v>
+        <v>650846</v>
       </c>
       <c r="R25" t="n">
         <v>7170647</v>
@@ -3224,10 +3249,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589847</v>
+        <v>121589836</v>
       </c>
       <c r="B26" t="n">
-        <v>79725</v>
+        <v>90746</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3236,25 +3261,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3268,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651045</v>
+        <v>651064</v>
       </c>
       <c r="R26" t="n">
-        <v>7170684</v>
+        <v>7170712</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3330,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589851</v>
+        <v>121589850</v>
       </c>
       <c r="B27" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3374,10 +3399,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650992</v>
+        <v>651040</v>
       </c>
       <c r="R27" t="n">
-        <v>7170679</v>
+        <v>7170694</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3436,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589861</v>
+        <v>121589851</v>
       </c>
       <c r="B28" t="n">
-        <v>98105</v>
+        <v>79697</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3448,30 +3473,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3480,10 +3505,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650816</v>
+        <v>650992</v>
       </c>
       <c r="R28" t="n">
-        <v>7170626</v>
+        <v>7170679</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3516,11 +3541,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3547,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589865</v>
+        <v>121589854</v>
       </c>
       <c r="B29" t="n">
-        <v>79690</v>
+        <v>79726</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3559,25 +3579,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3591,10 +3611,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650742</v>
+        <v>650895</v>
       </c>
       <c r="R29" t="n">
-        <v>7170597</v>
+        <v>7170701</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3627,11 +3647,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3658,10 +3673,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121589831</v>
+        <v>121589817</v>
       </c>
       <c r="B30" t="n">
-        <v>90738</v>
+        <v>98113</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3670,30 +3685,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3702,10 +3717,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650882</v>
+        <v>650754</v>
       </c>
       <c r="R30" t="n">
-        <v>7170828</v>
+        <v>7170637</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3764,10 +3779,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121589857</v>
+        <v>121589829</v>
       </c>
       <c r="B31" t="n">
-        <v>90716</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3780,21 +3795,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3808,10 +3823,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650826</v>
+        <v>650789</v>
       </c>
       <c r="R31" t="n">
-        <v>7170658</v>
+        <v>7170866</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3844,11 +3859,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121589834</v>
+        <v>121589863</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3919,10 +3929,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650935</v>
+        <v>650786</v>
       </c>
       <c r="R32" t="n">
-        <v>7170775</v>
+        <v>7170620</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3981,10 +3991,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121589842</v>
+        <v>121589837</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4025,10 +4035,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651053</v>
+        <v>651072</v>
       </c>
       <c r="R33" t="n">
-        <v>7170636</v>
+        <v>7170724</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4087,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121589833</v>
+        <v>121589852</v>
       </c>
       <c r="B34" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4122,7 +4132,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4131,10 +4141,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650931</v>
+        <v>650913</v>
       </c>
       <c r="R34" t="n">
-        <v>7170785</v>
+        <v>7170668</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4196,7 +4206,7 @@
         <v>121589830</v>
       </c>
       <c r="B35" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4299,10 +4309,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121589836</v>
+        <v>121589839</v>
       </c>
       <c r="B36" t="n">
-        <v>90738</v>
+        <v>79697</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4315,21 +4325,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4343,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651064</v>
+        <v>651123</v>
       </c>
       <c r="R36" t="n">
-        <v>7170712</v>
+        <v>7170655</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4405,10 +4415,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121589819</v>
+        <v>121589838</v>
       </c>
       <c r="B37" t="n">
-        <v>79725</v>
+        <v>79726</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4421,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4449,10 +4459,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650739</v>
+        <v>651123</v>
       </c>
       <c r="R37" t="n">
-        <v>7170646</v>
+        <v>7170655</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4511,10 +4521,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121589840</v>
+        <v>121589828</v>
       </c>
       <c r="B38" t="n">
-        <v>57509</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4527,21 +4537,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4549,24 +4559,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651113</v>
+        <v>650645</v>
       </c>
       <c r="R38" t="n">
-        <v>7170655</v>
+        <v>7170985</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4599,11 +4601,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4630,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121589856</v>
+        <v>121589820</v>
       </c>
       <c r="B39" t="n">
-        <v>98022</v>
+        <v>79697</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4642,25 +4639,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4674,10 +4671,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650844</v>
+        <v>650739</v>
       </c>
       <c r="R39" t="n">
-        <v>7170673</v>
+        <v>7170646</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4736,10 +4733,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121589855</v>
+        <v>121589849</v>
       </c>
       <c r="B40" t="n">
-        <v>79690</v>
+        <v>79726</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4748,25 +4745,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4780,10 +4777,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650892</v>
+        <v>651041</v>
       </c>
       <c r="R40" t="n">
-        <v>7170693</v>
+        <v>7170695</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4816,11 +4813,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4847,10 +4839,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121589846</v>
+        <v>121589840</v>
       </c>
       <c r="B41" t="n">
-        <v>79690</v>
+        <v>57510</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4863,21 +4855,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4885,16 +4877,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651020</v>
+        <v>651113</v>
       </c>
       <c r="R41" t="n">
-        <v>7170657</v>
+        <v>7170655</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer på rönn</t>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4958,10 +4958,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121589850</v>
+        <v>121589842</v>
       </c>
       <c r="B42" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651040</v>
+        <v>651053</v>
       </c>
       <c r="R42" t="n">
-        <v>7170694</v>
+        <v>7170636</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121589862</v>
+        <v>121589848</v>
       </c>
       <c r="B43" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5080,21 +5080,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650799</v>
+        <v>651044</v>
       </c>
       <c r="R43" t="n">
-        <v>7170628</v>
+        <v>7170685</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>

--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589844</v>
+        <v>121589856</v>
       </c>
       <c r="B4" t="n">
-        <v>90894</v>
+        <v>98030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1588</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651065</v>
+        <v>650844</v>
       </c>
       <c r="R4" t="n">
-        <v>7170686</v>
+        <v>7170673</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589856</v>
+        <v>121589844</v>
       </c>
       <c r="B5" t="n">
-        <v>98030</v>
+        <v>90894</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>1588</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650844</v>
+        <v>651065</v>
       </c>
       <c r="R5" t="n">
-        <v>7170673</v>
+        <v>7170686</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589857</v>
+        <v>121589819</v>
       </c>
       <c r="B9" t="n">
-        <v>90724</v>
+        <v>79732</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650826</v>
+        <v>650739</v>
       </c>
       <c r="R9" t="n">
-        <v>7170658</v>
+        <v>7170646</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1497,11 +1497,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589819</v>
+        <v>121589864</v>
       </c>
       <c r="B10" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1572,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650739</v>
+        <v>650742</v>
       </c>
       <c r="R10" t="n">
-        <v>7170646</v>
+        <v>7170597</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1634,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589864</v>
+        <v>121589853</v>
       </c>
       <c r="B11" t="n">
         <v>79733</v>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650742</v>
+        <v>650880</v>
       </c>
       <c r="R11" t="n">
-        <v>7170597</v>
+        <v>7170682</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589853</v>
+        <v>121589847</v>
       </c>
       <c r="B12" t="n">
-        <v>79733</v>
+        <v>79732</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1784,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650880</v>
+        <v>651045</v>
       </c>
       <c r="R12" t="n">
-        <v>7170682</v>
+        <v>7170684</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589847</v>
+        <v>121589857</v>
       </c>
       <c r="B13" t="n">
-        <v>79732</v>
+        <v>90724</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1890,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651045</v>
+        <v>650826</v>
       </c>
       <c r="R13" t="n">
-        <v>7170684</v>
+        <v>7170658</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1926,6 +1921,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589834</v>
+        <v>121589859</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650935</v>
+        <v>650836</v>
       </c>
       <c r="R17" t="n">
-        <v>7170775</v>
+        <v>7170651</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589865</v>
+        <v>121589834</v>
       </c>
       <c r="B18" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,21 +2397,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650742</v>
+        <v>650935</v>
       </c>
       <c r="R18" t="n">
-        <v>7170597</v>
+        <v>7170775</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2461,11 +2461,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589859</v>
+        <v>121589865</v>
       </c>
       <c r="B19" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2536,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650836</v>
+        <v>650742</v>
       </c>
       <c r="R19" t="n">
-        <v>7170651</v>
+        <v>7170597</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2572,6 +2567,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589841</v>
+        <v>121589845</v>
       </c>
       <c r="B20" t="n">
-        <v>79698</v>
+        <v>79733</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,25 +2610,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651098</v>
+        <v>651040</v>
       </c>
       <c r="R20" t="n">
-        <v>7170643</v>
+        <v>7170672</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2678,6 +2678,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589845</v>
+        <v>121589841</v>
       </c>
       <c r="B21" t="n">
-        <v>79733</v>
+        <v>79698</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,25 +2721,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2748,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651040</v>
+        <v>651098</v>
       </c>
       <c r="R21" t="n">
-        <v>7170672</v>
+        <v>7170643</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2784,11 +2789,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4203,10 +4203,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121589830</v>
+        <v>121589839</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4219,21 +4219,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650815</v>
+        <v>651123</v>
       </c>
       <c r="R35" t="n">
-        <v>7170874</v>
+        <v>7170655</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4309,10 +4309,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121589839</v>
+        <v>121589838</v>
       </c>
       <c r="B36" t="n">
-        <v>79697</v>
+        <v>79726</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4321,25 +4321,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4415,10 +4415,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121589838</v>
+        <v>121589830</v>
       </c>
       <c r="B37" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4427,25 +4427,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651123</v>
+        <v>650815</v>
       </c>
       <c r="R37" t="n">
-        <v>7170655</v>
+        <v>7170874</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121589828</v>
+        <v>121589840</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4537,21 +4537,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4559,16 +4559,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650645</v>
+        <v>651113</v>
       </c>
       <c r="R38" t="n">
-        <v>7170985</v>
+        <v>7170655</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4601,6 +4609,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4627,10 +4640,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121589820</v>
+        <v>121589828</v>
       </c>
       <c r="B39" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4643,21 +4656,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4671,10 +4684,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650739</v>
+        <v>650645</v>
       </c>
       <c r="R39" t="n">
-        <v>7170646</v>
+        <v>7170985</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4733,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121589849</v>
+        <v>121589820</v>
       </c>
       <c r="B40" t="n">
-        <v>79726</v>
+        <v>79697</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4745,25 +4758,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4777,10 +4790,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651041</v>
+        <v>650739</v>
       </c>
       <c r="R40" t="n">
-        <v>7170695</v>
+        <v>7170646</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4839,10 +4852,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121589840</v>
+        <v>121589849</v>
       </c>
       <c r="B41" t="n">
-        <v>57510</v>
+        <v>79726</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4851,25 +4864,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4877,24 +4890,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651113</v>
+        <v>651041</v>
       </c>
       <c r="R41" t="n">
-        <v>7170655</v>
+        <v>7170695</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4927,11 +4932,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589856</v>
+        <v>121589844</v>
       </c>
       <c r="B4" t="n">
-        <v>98030</v>
+        <v>90894</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>1588</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650844</v>
+        <v>651065</v>
       </c>
       <c r="R4" t="n">
-        <v>7170673</v>
+        <v>7170686</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589844</v>
+        <v>121589856</v>
       </c>
       <c r="B5" t="n">
-        <v>90894</v>
+        <v>98030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1588</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651065</v>
+        <v>650844</v>
       </c>
       <c r="R5" t="n">
-        <v>7170686</v>
+        <v>7170673</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589859</v>
+        <v>121589834</v>
       </c>
       <c r="B17" t="n">
-        <v>90724</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650836</v>
+        <v>650935</v>
       </c>
       <c r="R17" t="n">
-        <v>7170651</v>
+        <v>7170775</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589834</v>
+        <v>121589865</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,21 +2397,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650935</v>
+        <v>650742</v>
       </c>
       <c r="R18" t="n">
-        <v>7170775</v>
+        <v>7170597</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2461,6 +2461,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589865</v>
+        <v>121589859</v>
       </c>
       <c r="B19" t="n">
-        <v>79697</v>
+        <v>90724</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2503,21 +2508,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650742</v>
+        <v>650836</v>
       </c>
       <c r="R19" t="n">
-        <v>7170597</v>
+        <v>7170651</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2567,11 +2572,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589845</v>
+        <v>121589841</v>
       </c>
       <c r="B20" t="n">
-        <v>79733</v>
+        <v>79698</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,25 +2610,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651040</v>
+        <v>651098</v>
       </c>
       <c r="R20" t="n">
-        <v>7170672</v>
+        <v>7170643</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2678,11 +2678,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2709,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589841</v>
+        <v>121589845</v>
       </c>
       <c r="B21" t="n">
-        <v>79698</v>
+        <v>79733</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,25 +2716,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2753,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651098</v>
+        <v>651040</v>
       </c>
       <c r="R21" t="n">
-        <v>7170643</v>
+        <v>7170672</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2789,6 +2784,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589834</v>
+        <v>121589858</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650935</v>
+        <v>650846</v>
       </c>
       <c r="R2" t="n">
-        <v>7170775</v>
+        <v>7170647</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589851</v>
+        <v>121589860</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650992</v>
+        <v>650830</v>
       </c>
       <c r="R3" t="n">
-        <v>7170679</v>
+        <v>7170622</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589865</v>
+        <v>121589850</v>
       </c>
       <c r="B4" t="n">
         <v>79697</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650742</v>
+        <v>651040</v>
       </c>
       <c r="R4" t="n">
-        <v>7170597</v>
+        <v>7170694</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,11 +967,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589835</v>
+        <v>121589859</v>
       </c>
       <c r="B5" t="n">
-        <v>97067</v>
+        <v>90724</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651023</v>
+        <v>650836</v>
       </c>
       <c r="R5" t="n">
-        <v>7170755</v>
+        <v>7170651</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589836</v>
+        <v>121589844</v>
       </c>
       <c r="B6" t="n">
-        <v>90746</v>
+        <v>90894</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651064</v>
+        <v>651065</v>
       </c>
       <c r="R6" t="n">
-        <v>7170712</v>
+        <v>7170686</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589820</v>
+        <v>121589843</v>
       </c>
       <c r="B7" t="n">
         <v>79697</v>
@@ -1254,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650739</v>
+        <v>651069</v>
       </c>
       <c r="R7" t="n">
-        <v>7170646</v>
+        <v>7170647</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589841</v>
+        <v>121589861</v>
       </c>
       <c r="B8" t="n">
-        <v>79698</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,30 +1323,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1360,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651098</v>
+        <v>650816</v>
       </c>
       <c r="R8" t="n">
-        <v>7170643</v>
+        <v>7170626</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1396,6 +1391,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589832</v>
+        <v>121589838</v>
       </c>
       <c r="B9" t="n">
-        <v>90894</v>
+        <v>79726</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1588</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650886</v>
+        <v>651123</v>
       </c>
       <c r="R9" t="n">
-        <v>7170833</v>
+        <v>7170655</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589828</v>
+        <v>121589841</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650645</v>
+        <v>651098</v>
       </c>
       <c r="R10" t="n">
-        <v>7170985</v>
+        <v>7170643</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589831</v>
+        <v>121589839</v>
       </c>
       <c r="B11" t="n">
-        <v>90746</v>
+        <v>79697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650882</v>
+        <v>651123</v>
       </c>
       <c r="R11" t="n">
-        <v>7170828</v>
+        <v>7170655</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589830</v>
+        <v>121589852</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,30 +1752,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650815</v>
+        <v>650913</v>
       </c>
       <c r="R12" t="n">
-        <v>7170874</v>
+        <v>7170668</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589847</v>
+        <v>121589835</v>
       </c>
       <c r="B13" t="n">
-        <v>79732</v>
+        <v>97067</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651045</v>
+        <v>651023</v>
       </c>
       <c r="R13" t="n">
-        <v>7170684</v>
+        <v>7170755</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589833</v>
+        <v>121589818</v>
       </c>
       <c r="B14" t="n">
         <v>98113</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650931</v>
+        <v>650745</v>
       </c>
       <c r="R14" t="n">
-        <v>7170785</v>
+        <v>7170644</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589861</v>
+        <v>121589854</v>
       </c>
       <c r="B15" t="n">
-        <v>98113</v>
+        <v>79726</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,30 +2070,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650816</v>
+        <v>650895</v>
       </c>
       <c r="R15" t="n">
-        <v>7170626</v>
+        <v>7170701</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2138,11 +2138,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589844</v>
+        <v>121589845</v>
       </c>
       <c r="B16" t="n">
-        <v>90894</v>
+        <v>79733</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1588</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2213,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651065</v>
+        <v>651040</v>
       </c>
       <c r="R16" t="n">
-        <v>7170686</v>
+        <v>7170672</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2249,6 +2244,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589846</v>
+        <v>121589834</v>
       </c>
       <c r="B17" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651020</v>
+        <v>650935</v>
       </c>
       <c r="R17" t="n">
-        <v>7170657</v>
+        <v>7170775</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2355,11 +2355,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2386,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589854</v>
+        <v>121589831</v>
       </c>
       <c r="B18" t="n">
-        <v>79726</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,25 +2393,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2430,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650895</v>
+        <v>650882</v>
       </c>
       <c r="R18" t="n">
-        <v>7170701</v>
+        <v>7170828</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2492,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589855</v>
+        <v>121589817</v>
       </c>
       <c r="B19" t="n">
-        <v>79697</v>
+        <v>98113</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,30 +2499,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2536,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650892</v>
+        <v>650754</v>
       </c>
       <c r="R19" t="n">
-        <v>7170693</v>
+        <v>7170637</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2572,11 +2567,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,10 +2593,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589864</v>
+        <v>121589833</v>
       </c>
       <c r="B20" t="n">
-        <v>79733</v>
+        <v>98113</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,30 +2605,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2647,10 +2637,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650742</v>
+        <v>650931</v>
       </c>
       <c r="R20" t="n">
-        <v>7170597</v>
+        <v>7170785</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2709,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589849</v>
+        <v>121589832</v>
       </c>
       <c r="B21" t="n">
-        <v>79726</v>
+        <v>90894</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,25 +2711,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>1588</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2753,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651041</v>
+        <v>650886</v>
       </c>
       <c r="R21" t="n">
-        <v>7170695</v>
+        <v>7170833</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2815,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589856</v>
+        <v>121589851</v>
       </c>
       <c r="B22" t="n">
-        <v>98030</v>
+        <v>79697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,25 +2817,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2859,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650844</v>
+        <v>650992</v>
       </c>
       <c r="R22" t="n">
-        <v>7170673</v>
+        <v>7170679</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2921,10 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589839</v>
+        <v>121589863</v>
       </c>
       <c r="B23" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,21 +2927,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2965,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651123</v>
+        <v>650786</v>
       </c>
       <c r="R23" t="n">
-        <v>7170655</v>
+        <v>7170620</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3027,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589857</v>
+        <v>121589865</v>
       </c>
       <c r="B24" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3071,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650826</v>
+        <v>650742</v>
       </c>
       <c r="R24" t="n">
-        <v>7170658</v>
+        <v>7170597</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3111,7 +3101,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar på stående död gran</t>
+          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3138,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589859</v>
+        <v>121589847</v>
       </c>
       <c r="B25" t="n">
-        <v>90724</v>
+        <v>79732</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,25 +3140,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3182,10 +3172,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650836</v>
+        <v>651045</v>
       </c>
       <c r="R25" t="n">
-        <v>7170651</v>
+        <v>7170684</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3244,7 +3234,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589837</v>
+        <v>121589830</v>
       </c>
       <c r="B26" t="n">
         <v>78616</v>
@@ -3288,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651072</v>
+        <v>650815</v>
       </c>
       <c r="R26" t="n">
-        <v>7170724</v>
+        <v>7170874</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3350,10 +3340,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589818</v>
+        <v>121589856</v>
       </c>
       <c r="B27" t="n">
-        <v>98113</v>
+        <v>98030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3362,30 +3352,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3394,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650745</v>
+        <v>650844</v>
       </c>
       <c r="R27" t="n">
-        <v>7170644</v>
+        <v>7170673</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3456,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589862</v>
+        <v>121589820</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3472,21 +3462,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3500,10 +3490,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650799</v>
+        <v>650739</v>
       </c>
       <c r="R28" t="n">
-        <v>7170628</v>
+        <v>7170646</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3562,10 +3552,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589840</v>
+        <v>121589819</v>
       </c>
       <c r="B29" t="n">
-        <v>57510</v>
+        <v>79732</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3574,25 +3564,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3600,24 +3590,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651113</v>
+        <v>650739</v>
       </c>
       <c r="R29" t="n">
-        <v>7170655</v>
+        <v>7170646</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3650,11 +3632,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3681,10 +3658,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121589845</v>
+        <v>121589828</v>
       </c>
       <c r="B30" t="n">
-        <v>79733</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3693,25 +3670,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3725,10 +3702,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651040</v>
+        <v>650645</v>
       </c>
       <c r="R30" t="n">
-        <v>7170672</v>
+        <v>7170985</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3761,11 +3738,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3792,10 +3764,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121589848</v>
+        <v>121589842</v>
       </c>
       <c r="B31" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3808,21 +3780,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3836,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651044</v>
+        <v>651053</v>
       </c>
       <c r="R31" t="n">
-        <v>7170685</v>
+        <v>7170636</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3898,10 +3870,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121589829</v>
+        <v>121589849</v>
       </c>
       <c r="B32" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3910,25 +3882,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3942,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650789</v>
+        <v>651041</v>
       </c>
       <c r="R32" t="n">
-        <v>7170866</v>
+        <v>7170695</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4004,10 +3976,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121589819</v>
+        <v>121589853</v>
       </c>
       <c r="B33" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4020,21 +3992,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4048,10 +4020,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650739</v>
+        <v>650880</v>
       </c>
       <c r="R33" t="n">
-        <v>7170646</v>
+        <v>7170682</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4110,10 +4082,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121589838</v>
+        <v>121589836</v>
       </c>
       <c r="B34" t="n">
-        <v>79726</v>
+        <v>90746</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4122,25 +4094,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4154,10 +4126,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651123</v>
+        <v>651064</v>
       </c>
       <c r="R34" t="n">
-        <v>7170655</v>
+        <v>7170712</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4216,10 +4188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121589853</v>
+        <v>121589855</v>
       </c>
       <c r="B35" t="n">
-        <v>79733</v>
+        <v>79697</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4228,25 +4200,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4260,10 +4232,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650880</v>
+        <v>650892</v>
       </c>
       <c r="R35" t="n">
-        <v>7170682</v>
+        <v>7170693</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4296,6 +4268,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4322,7 +4299,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121589842</v>
+        <v>121589829</v>
       </c>
       <c r="B36" t="n">
         <v>78616</v>
@@ -4366,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651053</v>
+        <v>650789</v>
       </c>
       <c r="R36" t="n">
-        <v>7170636</v>
+        <v>7170866</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4428,10 +4405,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121589817</v>
+        <v>121589862</v>
       </c>
       <c r="B37" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4440,30 +4417,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4472,10 +4449,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650754</v>
+        <v>650799</v>
       </c>
       <c r="R37" t="n">
-        <v>7170637</v>
+        <v>7170628</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4534,10 +4511,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121589852</v>
+        <v>121589837</v>
       </c>
       <c r="B38" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,30 +4523,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4578,10 +4555,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650913</v>
+        <v>651072</v>
       </c>
       <c r="R38" t="n">
-        <v>7170668</v>
+        <v>7170724</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4640,7 +4617,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121589850</v>
+        <v>121589846</v>
       </c>
       <c r="B39" t="n">
         <v>79697</v>
@@ -4684,10 +4661,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651040</v>
+        <v>651020</v>
       </c>
       <c r="R39" t="n">
-        <v>7170694</v>
+        <v>7170657</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4720,6 +4697,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4746,7 +4728,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121589843</v>
+        <v>121589848</v>
       </c>
       <c r="B40" t="n">
         <v>79697</v>
@@ -4790,10 +4772,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651069</v>
+        <v>651044</v>
       </c>
       <c r="R40" t="n">
-        <v>7170647</v>
+        <v>7170685</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4852,10 +4834,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121589863</v>
+        <v>121589840</v>
       </c>
       <c r="B41" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4868,21 +4850,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4890,16 +4872,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650786</v>
+        <v>651113</v>
       </c>
       <c r="R41" t="n">
-        <v>7170620</v>
+        <v>7170655</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4932,6 +4922,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4958,10 +4953,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121589858</v>
+        <v>121589857</v>
       </c>
       <c r="B42" t="n">
-        <v>98113</v>
+        <v>90724</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4970,30 +4965,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5002,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650846</v>
+        <v>650826</v>
       </c>
       <c r="R42" t="n">
-        <v>7170647</v>
+        <v>7170658</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5038,6 +5033,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5064,10 +5064,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121589860</v>
+        <v>121589864</v>
       </c>
       <c r="B43" t="n">
-        <v>98113</v>
+        <v>79733</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5076,30 +5076,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650830</v>
+        <v>650742</v>
       </c>
       <c r="R43" t="n">
-        <v>7170622</v>
+        <v>7170597</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>

--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -2487,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589817</v>
+        <v>121589832</v>
       </c>
       <c r="B19" t="n">
-        <v>98113</v>
+        <v>90894</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,30 +2499,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650754</v>
+        <v>650886</v>
       </c>
       <c r="R19" t="n">
-        <v>7170637</v>
+        <v>7170833</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2593,7 +2593,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589833</v>
+        <v>121589817</v>
       </c>
       <c r="B20" t="n">
         <v>98113</v>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650931</v>
+        <v>650754</v>
       </c>
       <c r="R20" t="n">
-        <v>7170785</v>
+        <v>7170637</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589832</v>
+        <v>121589833</v>
       </c>
       <c r="B21" t="n">
-        <v>90894</v>
+        <v>98113</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,30 +2711,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650886</v>
+        <v>650931</v>
       </c>
       <c r="R21" t="n">
-        <v>7170833</v>
+        <v>7170785</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589820</v>
+        <v>121589828</v>
       </c>
       <c r="B28" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3462,21 +3462,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650739</v>
+        <v>650645</v>
       </c>
       <c r="R28" t="n">
-        <v>7170646</v>
+        <v>7170985</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589819</v>
+        <v>121589842</v>
       </c>
       <c r="B29" t="n">
-        <v>79732</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3564,20 +3564,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650739</v>
+        <v>651053</v>
       </c>
       <c r="R29" t="n">
-        <v>7170646</v>
+        <v>7170636</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121589828</v>
+        <v>121589820</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650645</v>
+        <v>650739</v>
       </c>
       <c r="R30" t="n">
-        <v>7170985</v>
+        <v>7170646</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3764,10 +3764,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121589842</v>
+        <v>121589819</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
+        <v>79732</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3776,20 +3776,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651053</v>
+        <v>650739</v>
       </c>
       <c r="R31" t="n">
-        <v>7170636</v>
+        <v>7170646</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121589855</v>
+        <v>121589829</v>
       </c>
       <c r="B35" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650892</v>
+        <v>650789</v>
       </c>
       <c r="R35" t="n">
-        <v>7170693</v>
+        <v>7170866</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4268,11 +4268,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4299,10 +4294,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121589829</v>
+        <v>121589855</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4315,21 +4310,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4343,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650789</v>
+        <v>650892</v>
       </c>
       <c r="R36" t="n">
-        <v>7170866</v>
+        <v>7170693</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4379,6 +4374,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4834,10 +4834,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121589840</v>
+        <v>121589864</v>
       </c>
       <c r="B41" t="n">
-        <v>57510</v>
+        <v>79733</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4846,25 +4846,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4872,24 +4872,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651113</v>
+        <v>650742</v>
       </c>
       <c r="R41" t="n">
-        <v>7170655</v>
+        <v>7170597</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4922,11 +4914,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,10 +4940,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121589857</v>
+        <v>121589840</v>
       </c>
       <c r="B42" t="n">
-        <v>90724</v>
+        <v>57510</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4969,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4991,16 +4978,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650826</v>
+        <v>651113</v>
       </c>
       <c r="R42" t="n">
-        <v>7170658</v>
+        <v>7170655</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5037,7 +5032,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar på stående död gran</t>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5064,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121589864</v>
+        <v>121589857</v>
       </c>
       <c r="B43" t="n">
-        <v>79733</v>
+        <v>90724</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5076,25 +5071,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5108,10 +5103,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650742</v>
+        <v>650826</v>
       </c>
       <c r="R43" t="n">
-        <v>7170597</v>
+        <v>7170658</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5144,6 +5139,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589858</v>
+        <v>121589852</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650846</v>
+        <v>650913</v>
       </c>
       <c r="R2" t="n">
-        <v>7170647</v>
+        <v>7170668</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589860</v>
+        <v>121589859</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>90724</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650830</v>
+        <v>650836</v>
       </c>
       <c r="R3" t="n">
-        <v>7170622</v>
+        <v>7170651</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589850</v>
+        <v>121589843</v>
       </c>
       <c r="B4" t="n">
         <v>79697</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651040</v>
+        <v>651069</v>
       </c>
       <c r="R4" t="n">
-        <v>7170694</v>
+        <v>7170647</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589859</v>
+        <v>121589846</v>
       </c>
       <c r="B5" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650836</v>
+        <v>651020</v>
       </c>
       <c r="R5" t="n">
-        <v>7170651</v>
+        <v>7170657</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589844</v>
+        <v>121589832</v>
       </c>
       <c r="B6" t="n">
         <v>90894</v>
@@ -1143,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651065</v>
+        <v>650886</v>
       </c>
       <c r="R6" t="n">
-        <v>7170686</v>
+        <v>7170833</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589843</v>
+        <v>121589836</v>
       </c>
       <c r="B7" t="n">
-        <v>79697</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651069</v>
+        <v>651064</v>
       </c>
       <c r="R7" t="n">
-        <v>7170647</v>
+        <v>7170712</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589861</v>
+        <v>121589848</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>79697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,30 +1328,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1355,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650816</v>
+        <v>651044</v>
       </c>
       <c r="R8" t="n">
-        <v>7170626</v>
+        <v>7170685</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1391,11 +1396,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589838</v>
+        <v>121589818</v>
       </c>
       <c r="B9" t="n">
-        <v>79726</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,30 +1434,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651123</v>
+        <v>650745</v>
       </c>
       <c r="R9" t="n">
-        <v>7170655</v>
+        <v>7170644</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589841</v>
+        <v>121589856</v>
       </c>
       <c r="B10" t="n">
-        <v>79698</v>
+        <v>98030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651098</v>
+        <v>650844</v>
       </c>
       <c r="R10" t="n">
-        <v>7170643</v>
+        <v>7170673</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589852</v>
+        <v>121589834</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,30 +1752,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650913</v>
+        <v>650935</v>
       </c>
       <c r="R12" t="n">
-        <v>7170668</v>
+        <v>7170775</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589835</v>
+        <v>121589830</v>
       </c>
       <c r="B13" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651023</v>
+        <v>650815</v>
       </c>
       <c r="R13" t="n">
-        <v>7170755</v>
+        <v>7170874</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589818</v>
+        <v>121589849</v>
       </c>
       <c r="B14" t="n">
-        <v>98113</v>
+        <v>79726</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,30 +1964,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650745</v>
+        <v>651041</v>
       </c>
       <c r="R14" t="n">
-        <v>7170644</v>
+        <v>7170695</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589845</v>
+        <v>121589828</v>
       </c>
       <c r="B16" t="n">
-        <v>79733</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651040</v>
+        <v>650645</v>
       </c>
       <c r="R16" t="n">
-        <v>7170672</v>
+        <v>7170985</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2244,11 +2244,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589834</v>
+        <v>121589864</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>79733</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2319,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650935</v>
+        <v>650742</v>
       </c>
       <c r="R17" t="n">
-        <v>7170775</v>
+        <v>7170597</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2381,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589831</v>
+        <v>121589860</v>
       </c>
       <c r="B18" t="n">
-        <v>90746</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,30 +2388,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2425,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650882</v>
+        <v>650830</v>
       </c>
       <c r="R18" t="n">
-        <v>7170828</v>
+        <v>7170622</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2487,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589832</v>
+        <v>121589835</v>
       </c>
       <c r="B19" t="n">
-        <v>90894</v>
+        <v>97067</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1588</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650886</v>
+        <v>651023</v>
       </c>
       <c r="R19" t="n">
-        <v>7170833</v>
+        <v>7170755</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2593,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589817</v>
+        <v>121589844</v>
       </c>
       <c r="B20" t="n">
-        <v>98113</v>
+        <v>90894</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2605,30 +2600,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2637,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650754</v>
+        <v>651065</v>
       </c>
       <c r="R20" t="n">
-        <v>7170637</v>
+        <v>7170686</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2699,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589833</v>
+        <v>121589841</v>
       </c>
       <c r="B21" t="n">
-        <v>98113</v>
+        <v>79698</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,30 +2706,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2743,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650931</v>
+        <v>651098</v>
       </c>
       <c r="R21" t="n">
-        <v>7170785</v>
+        <v>7170643</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2805,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589851</v>
+        <v>121589831</v>
       </c>
       <c r="B22" t="n">
-        <v>79697</v>
+        <v>90746</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2849,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650992</v>
+        <v>650882</v>
       </c>
       <c r="R22" t="n">
-        <v>7170679</v>
+        <v>7170828</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2911,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589863</v>
+        <v>121589845</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>79733</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,25 +2918,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2955,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650786</v>
+        <v>651040</v>
       </c>
       <c r="R23" t="n">
-        <v>7170620</v>
+        <v>7170672</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2991,6 +2986,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589865</v>
+        <v>121589833</v>
       </c>
       <c r="B24" t="n">
-        <v>79697</v>
+        <v>98113</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3029,30 +3029,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650742</v>
+        <v>650931</v>
       </c>
       <c r="R24" t="n">
-        <v>7170597</v>
+        <v>7170785</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3097,11 +3097,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589847</v>
+        <v>121589838</v>
       </c>
       <c r="B25" t="n">
-        <v>79732</v>
+        <v>79726</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3144,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3172,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651045</v>
+        <v>651123</v>
       </c>
       <c r="R25" t="n">
-        <v>7170684</v>
+        <v>7170655</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3234,10 +3229,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589830</v>
+        <v>121589858</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3246,30 +3241,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3278,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650815</v>
+        <v>650846</v>
       </c>
       <c r="R26" t="n">
-        <v>7170874</v>
+        <v>7170647</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3340,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589856</v>
+        <v>121589857</v>
       </c>
       <c r="B27" t="n">
-        <v>98030</v>
+        <v>90724</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3352,25 +3347,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3384,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650844</v>
+        <v>650826</v>
       </c>
       <c r="R27" t="n">
-        <v>7170673</v>
+        <v>7170658</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3420,6 +3415,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3446,7 +3446,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589828</v>
+        <v>121589842</v>
       </c>
       <c r="B28" t="n">
         <v>78616</v>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650645</v>
+        <v>651053</v>
       </c>
       <c r="R28" t="n">
-        <v>7170985</v>
+        <v>7170636</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589842</v>
+        <v>121589861</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3564,30 +3564,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651053</v>
+        <v>650816</v>
       </c>
       <c r="R29" t="n">
-        <v>7170636</v>
+        <v>7170626</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3632,6 +3632,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3658,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121589820</v>
+        <v>121589862</v>
       </c>
       <c r="B30" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3674,21 +3679,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3702,10 +3707,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650739</v>
+        <v>650799</v>
       </c>
       <c r="R30" t="n">
-        <v>7170646</v>
+        <v>7170628</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3764,10 +3769,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121589819</v>
+        <v>121589829</v>
       </c>
       <c r="B31" t="n">
-        <v>79732</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3776,20 +3781,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3808,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650739</v>
+        <v>650789</v>
       </c>
       <c r="R31" t="n">
-        <v>7170646</v>
+        <v>7170866</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3870,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121589849</v>
+        <v>121589819</v>
       </c>
       <c r="B32" t="n">
-        <v>79726</v>
+        <v>79732</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,21 +3891,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3914,10 +3919,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651041</v>
+        <v>650739</v>
       </c>
       <c r="R32" t="n">
-        <v>7170695</v>
+        <v>7170646</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4082,10 +4087,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121589836</v>
+        <v>121589840</v>
       </c>
       <c r="B34" t="n">
-        <v>90746</v>
+        <v>57510</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4098,21 +4103,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4120,16 +4125,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651064</v>
+        <v>651113</v>
       </c>
       <c r="R34" t="n">
-        <v>7170712</v>
+        <v>7170655</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4162,6 +4175,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4188,10 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121589829</v>
+        <v>121589817</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4200,30 +4218,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4232,10 +4250,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650789</v>
+        <v>650754</v>
       </c>
       <c r="R35" t="n">
-        <v>7170866</v>
+        <v>7170637</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4294,7 +4312,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121589855</v>
+        <v>121589850</v>
       </c>
       <c r="B36" t="n">
         <v>79697</v>
@@ -4338,10 +4356,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650892</v>
+        <v>651040</v>
       </c>
       <c r="R36" t="n">
-        <v>7170693</v>
+        <v>7170694</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4374,11 +4392,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121589862</v>
+        <v>121589820</v>
       </c>
       <c r="B37" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4421,21 +4434,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4449,10 +4462,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650799</v>
+        <v>650739</v>
       </c>
       <c r="R37" t="n">
-        <v>7170628</v>
+        <v>7170646</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4511,10 +4524,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121589837</v>
+        <v>121589851</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4527,21 +4540,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4555,10 +4568,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651072</v>
+        <v>650992</v>
       </c>
       <c r="R38" t="n">
-        <v>7170724</v>
+        <v>7170679</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4617,10 +4630,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121589846</v>
+        <v>121589847</v>
       </c>
       <c r="B39" t="n">
-        <v>79697</v>
+        <v>79732</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4629,25 +4642,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4661,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651020</v>
+        <v>651045</v>
       </c>
       <c r="R39" t="n">
-        <v>7170657</v>
+        <v>7170684</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4697,11 +4710,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4728,10 +4736,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121589848</v>
+        <v>121589863</v>
       </c>
       <c r="B40" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4744,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4772,10 +4780,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651044</v>
+        <v>650786</v>
       </c>
       <c r="R40" t="n">
-        <v>7170685</v>
+        <v>7170620</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4834,10 +4842,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121589864</v>
+        <v>121589855</v>
       </c>
       <c r="B41" t="n">
-        <v>79733</v>
+        <v>79697</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4846,25 +4854,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4878,10 +4886,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650742</v>
+        <v>650892</v>
       </c>
       <c r="R41" t="n">
-        <v>7170597</v>
+        <v>7170693</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4914,6 +4922,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4940,10 +4953,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121589840</v>
+        <v>121589837</v>
       </c>
       <c r="B42" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4956,21 +4969,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4978,24 +4991,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651113</v>
+        <v>651072</v>
       </c>
       <c r="R42" t="n">
-        <v>7170655</v>
+        <v>7170724</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5028,11 +5033,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121589857</v>
+        <v>121589865</v>
       </c>
       <c r="B43" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5075,21 +5075,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650826</v>
+        <v>650742</v>
       </c>
       <c r="R43" t="n">
-        <v>7170658</v>
+        <v>7170597</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar på stående död gran</t>
+          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589835</v>
+        <v>121589821</v>
       </c>
       <c r="B2" t="n">
-        <v>97085</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651023</v>
+        <v>650607</v>
       </c>
       <c r="R2" t="n">
-        <v>7170755</v>
+        <v>7170753</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589858</v>
+        <v>121589828</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,26 +787,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650846</v>
+        <v>650645</v>
       </c>
       <c r="R3" t="n">
-        <v>7170647</v>
+        <v>7170985</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,42 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589861</v>
+        <v>121589857</v>
       </c>
       <c r="B4" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650816</v>
+        <v>650826</v>
       </c>
       <c r="R4" t="n">
-        <v>7170626</v>
+        <v>7170658</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +956,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera blommar</t>
+          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589843</v>
+        <v>121589859</v>
       </c>
       <c r="B5" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651069</v>
+        <v>650836</v>
       </c>
       <c r="R5" t="n">
-        <v>7170647</v>
+        <v>7170651</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,37 +1084,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589853</v>
+        <v>121589832</v>
       </c>
       <c r="B6" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1148,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650880</v>
+        <v>650886</v>
       </c>
       <c r="R6" t="n">
-        <v>7170682</v>
+        <v>7170833</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589832</v>
+        <v>121589844</v>
       </c>
       <c r="B7" t="n">
-        <v>90908</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650886</v>
+        <v>651065</v>
       </c>
       <c r="R7" t="n">
-        <v>7170833</v>
+        <v>7170686</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589855</v>
+        <v>121589841</v>
       </c>
       <c r="B8" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1297,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1360,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650892</v>
+        <v>651098</v>
       </c>
       <c r="R8" t="n">
-        <v>7170693</v>
+        <v>7170643</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1396,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,37 +1387,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589859</v>
+        <v>121589829</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1471,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650836</v>
+        <v>650789</v>
       </c>
       <c r="R9" t="n">
-        <v>7170651</v>
+        <v>7170866</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,15 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589860</v>
+        <v>121589830</v>
       </c>
       <c r="B10" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,26 +1499,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1577,10 +1527,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650830</v>
+        <v>650815</v>
       </c>
       <c r="R10" t="n">
-        <v>7170622</v>
+        <v>7170874</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1639,19 +1589,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589862</v>
+        <v>121589834</v>
       </c>
       <c r="B11" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1683,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650799</v>
+        <v>650935</v>
       </c>
       <c r="R11" t="n">
-        <v>7170628</v>
+        <v>7170775</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,37 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589836</v>
+        <v>121589837</v>
       </c>
       <c r="B12" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651064</v>
+        <v>651072</v>
       </c>
       <c r="R12" t="n">
-        <v>7170712</v>
+        <v>7170724</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1851,32 +1791,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589819</v>
+        <v>121589842</v>
       </c>
       <c r="B13" t="n">
-        <v>79745</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1895,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650739</v>
+        <v>651053</v>
       </c>
       <c r="R13" t="n">
-        <v>7170646</v>
+        <v>7170636</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1957,19 +1892,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589842</v>
+        <v>121589862</v>
       </c>
       <c r="B14" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2001,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651053</v>
+        <v>650799</v>
       </c>
       <c r="R14" t="n">
-        <v>7170636</v>
+        <v>7170628</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2063,15 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589833</v>
+        <v>121589863</v>
       </c>
       <c r="B15" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2079,26 +2004,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2107,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650931</v>
+        <v>650786</v>
       </c>
       <c r="R15" t="n">
-        <v>7170785</v>
+        <v>7170620</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,15 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589830</v>
+        <v>121589820</v>
       </c>
       <c r="B16" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,21 +2105,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2213,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650815</v>
+        <v>650739</v>
       </c>
       <c r="R16" t="n">
-        <v>7170874</v>
+        <v>7170646</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2275,37 +2195,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589847</v>
+        <v>121589839</v>
       </c>
       <c r="B17" t="n">
-        <v>79745</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2319,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651045</v>
+        <v>651123</v>
       </c>
       <c r="R17" t="n">
-        <v>7170684</v>
+        <v>7170655</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2381,15 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589850</v>
+        <v>121589843</v>
       </c>
       <c r="B18" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,10 +2335,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651040</v>
+        <v>651069</v>
       </c>
       <c r="R18" t="n">
-        <v>7170694</v>
+        <v>7170647</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2487,15 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589831</v>
+        <v>121589846</v>
       </c>
       <c r="B19" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2408,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650882</v>
+        <v>651020</v>
       </c>
       <c r="R19" t="n">
-        <v>7170828</v>
+        <v>7170657</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2567,6 +2472,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,15 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589857</v>
+        <v>121589848</v>
       </c>
       <c r="B20" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2637,10 +2542,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650826</v>
+        <v>651044</v>
       </c>
       <c r="R20" t="n">
-        <v>7170658</v>
+        <v>7170685</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2673,11 +2578,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,37 +2604,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589849</v>
+        <v>121589850</v>
       </c>
       <c r="B21" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2748,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651041</v>
+        <v>651040</v>
       </c>
       <c r="R21" t="n">
-        <v>7170695</v>
+        <v>7170694</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2810,15 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589841</v>
+        <v>121589851</v>
       </c>
       <c r="B22" t="n">
-        <v>79711</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2854,10 +2744,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651098</v>
+        <v>650992</v>
       </c>
       <c r="R22" t="n">
-        <v>7170643</v>
+        <v>7170679</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2916,15 +2806,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589851</v>
+        <v>121589855</v>
       </c>
       <c r="B23" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2960,10 +2845,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650992</v>
+        <v>650892</v>
       </c>
       <c r="R23" t="n">
-        <v>7170679</v>
+        <v>7170693</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2996,6 +2881,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,15 +2912,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589829</v>
+        <v>121589865</v>
       </c>
       <c r="B24" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,21 +2923,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3066,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650789</v>
+        <v>650742</v>
       </c>
       <c r="R24" t="n">
-        <v>7170866</v>
+        <v>7170597</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3102,6 +2987,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,37 +3018,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589834</v>
+        <v>121589838</v>
       </c>
       <c r="B25" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3172,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650935</v>
+        <v>651123</v>
       </c>
       <c r="R25" t="n">
-        <v>7170775</v>
+        <v>7170655</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3234,15 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589854</v>
+        <v>121589849</v>
       </c>
       <c r="B26" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650895</v>
+        <v>651041</v>
       </c>
       <c r="R26" t="n">
-        <v>7170701</v>
+        <v>7170695</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3340,37 +3220,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589839</v>
+        <v>121589854</v>
       </c>
       <c r="B27" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3384,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651123</v>
+        <v>650895</v>
       </c>
       <c r="R27" t="n">
-        <v>7170655</v>
+        <v>7170701</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3446,32 +3321,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589837</v>
+        <v>121589819</v>
       </c>
       <c r="B28" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3490,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651072</v>
+        <v>650739</v>
       </c>
       <c r="R28" t="n">
-        <v>7170724</v>
+        <v>7170646</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3552,37 +3422,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589820</v>
+        <v>121589847</v>
       </c>
       <c r="B29" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3596,10 +3461,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650739</v>
+        <v>651045</v>
       </c>
       <c r="R29" t="n">
-        <v>7170646</v>
+        <v>7170684</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3658,15 +3523,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121589864</v>
+        <v>121589845</v>
       </c>
       <c r="B30" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3702,10 +3562,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650742</v>
+        <v>651040</v>
       </c>
       <c r="R30" t="n">
-        <v>7170597</v>
+        <v>7170672</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3738,6 +3598,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3764,37 +3629,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121589840</v>
+        <v>121589853</v>
       </c>
       <c r="B31" t="n">
-        <v>57518</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,24 +3662,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651113</v>
+        <v>650880</v>
       </c>
       <c r="R31" t="n">
-        <v>7170655</v>
+        <v>7170682</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3852,11 +3704,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,42 +3730,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121589817</v>
+        <v>121589864</v>
       </c>
       <c r="B32" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3927,10 +3769,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650754</v>
+        <v>650742</v>
       </c>
       <c r="R32" t="n">
-        <v>7170637</v>
+        <v>7170597</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3989,37 +3831,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121589856</v>
+        <v>121589840</v>
       </c>
       <c r="B33" t="n">
-        <v>98048</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4027,16 +3864,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650844</v>
+        <v>651113</v>
       </c>
       <c r="R33" t="n">
-        <v>7170673</v>
+        <v>7170655</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4069,6 +3914,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4095,15 +3945,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121589838</v>
+        <v>121589856</v>
       </c>
       <c r="B34" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4111,21 +3956,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4139,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651123</v>
+        <v>650844</v>
       </c>
       <c r="R34" t="n">
-        <v>7170655</v>
+        <v>7170673</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4201,42 +4046,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121589863</v>
+        <v>121589817</v>
       </c>
       <c r="B35" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4245,10 +4085,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650786</v>
+        <v>650754</v>
       </c>
       <c r="R35" t="n">
-        <v>7170620</v>
+        <v>7170637</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4307,42 +4147,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121589865</v>
+        <v>121589818</v>
       </c>
       <c r="B36" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4351,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650742</v>
+        <v>650745</v>
       </c>
       <c r="R36" t="n">
-        <v>7170597</v>
+        <v>7170644</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4387,11 +4222,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,42 +4248,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121589848</v>
+        <v>121589833</v>
       </c>
       <c r="B37" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4462,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651044</v>
+        <v>650931</v>
       </c>
       <c r="R37" t="n">
-        <v>7170685</v>
+        <v>7170785</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4524,42 +4349,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121589828</v>
+        <v>121589852</v>
       </c>
       <c r="B38" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4568,10 +4388,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650645</v>
+        <v>650913</v>
       </c>
       <c r="R38" t="n">
-        <v>7170985</v>
+        <v>7170668</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4630,42 +4450,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121589846</v>
+        <v>121589858</v>
       </c>
       <c r="B39" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4674,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651020</v>
+        <v>650846</v>
       </c>
       <c r="R39" t="n">
-        <v>7170657</v>
+        <v>7170647</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4710,11 +4525,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,15 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121589852</v>
+        <v>121589860</v>
       </c>
       <c r="B40" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,7 +4581,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4785,10 +4590,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650913</v>
+        <v>650830</v>
       </c>
       <c r="R40" t="n">
-        <v>7170668</v>
+        <v>7170622</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4847,42 +4652,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121589844</v>
+        <v>121589861</v>
       </c>
       <c r="B41" t="n">
-        <v>90908</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4891,10 +4691,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651065</v>
+        <v>650816</v>
       </c>
       <c r="R41" t="n">
-        <v>7170686</v>
+        <v>7170626</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4927,6 +4727,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,42 +4758,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121589818</v>
+        <v>121589835</v>
       </c>
       <c r="B42" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4997,10 +4797,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650745</v>
+        <v>651023</v>
       </c>
       <c r="R42" t="n">
-        <v>7170644</v>
+        <v>7170755</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5056,117 +4856,6 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>121589845</v>
-      </c>
-      <c r="B43" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Fäboliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>651040</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7170672</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53141-2024 artfynd.xlsx
+++ b/artfynd/A 53141-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589857</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589859</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589832</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589844</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589841</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589821</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589828</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589829</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589830</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589834</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589837</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589842</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589862</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589863</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589820</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589839</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589843</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2500,6 +2590,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589846</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2601,6 +2696,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589848</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,6 +2802,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589850</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589851</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2909,6 +3019,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589855</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3015,6 +3130,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589865</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3116,6 +3236,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589838</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3217,6 +3342,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589849</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3318,6 +3448,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589854</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3419,6 +3554,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589819</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3520,6 +3660,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589847</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3626,6 +3771,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589845</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3727,6 +3877,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589853</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3828,6 +3983,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589864</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3942,6 +4102,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589840</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4043,6 +4208,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589856</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4144,6 +4314,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589817</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4245,6 +4420,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589818</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4346,6 +4526,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589833</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4447,6 +4632,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589852</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4548,6 +4738,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589858</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4649,6 +4844,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589860</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4755,6 +4955,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589861</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4856,8 +5061,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589835</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>